--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,49 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R6" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,45 +1215,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595642</v>
+        <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707688</v>
+        <v>707781</v>
       </c>
       <c r="R7" t="n">
-        <v>6666281</v>
+        <v>6666273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595623</v>
+        <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>100916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707785</v>
+        <v>707688</v>
       </c>
       <c r="R8" t="n">
-        <v>6666294</v>
+        <v>6666281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>92843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R9" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>92843</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R10" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B9" t="n">
-        <v>92843</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R9" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>92843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R10" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,45 +1108,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R6" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,49 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>100916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R7" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595642</v>
+        <v>129595623</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707688</v>
+        <v>707785</v>
       </c>
       <c r="R8" t="n">
-        <v>6666281</v>
+        <v>6666294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,49 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R6" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,45 +1215,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595642</v>
+        <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707688</v>
+        <v>707781</v>
       </c>
       <c r="R7" t="n">
-        <v>6666281</v>
+        <v>6666273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595623</v>
+        <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>100916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707785</v>
+        <v>707688</v>
       </c>
       <c r="R8" t="n">
-        <v>6666294</v>
+        <v>6666281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>92871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R9" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>92843</v>
+        <v>91354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R10" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,45 +1108,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B6" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R6" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,49 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>100957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R7" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595642</v>
+        <v>129595623</v>
       </c>
       <c r="B8" t="n">
-        <v>100945</v>
+        <v>91587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707688</v>
+        <v>707785</v>
       </c>
       <c r="R8" t="n">
-        <v>6666281</v>
+        <v>6666294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>92871</v>
+        <v>92877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,49 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>100958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R6" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595642</v>
+        <v>129595623</v>
       </c>
       <c r="B7" t="n">
-        <v>100957</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707688</v>
+        <v>707785</v>
       </c>
       <c r="R7" t="n">
-        <v>6666281</v>
+        <v>6666294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,45 +1322,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B8" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R8" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,6 +1415,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>92877</v>
+        <v>92878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595642</v>
+        <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>100958</v>
+        <v>91588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707688</v>
+        <v>707785</v>
       </c>
       <c r="R6" t="n">
-        <v>6666281</v>
+        <v>6666294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,45 +1215,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R7" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,49 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R8" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1416,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>92878</v>
+        <v>92883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B9" t="n">
-        <v>92883</v>
+        <v>91366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R9" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B10" t="n">
-        <v>91366</v>
+        <v>92883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R10" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595623</v>
+        <v>129595642</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>100963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707785</v>
+        <v>707688</v>
       </c>
       <c r="R6" t="n">
-        <v>6666294</v>
+        <v>6666281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595642</v>
+        <v>129595623</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707688</v>
+        <v>707785</v>
       </c>
       <c r="R8" t="n">
-        <v>6666281</v>
+        <v>6666294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,45 +1108,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595642</v>
+        <v>129595630</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707688</v>
+        <v>707781</v>
       </c>
       <c r="R6" t="n">
-        <v>6666281</v>
+        <v>6666273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,49 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R7" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,49 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R6" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,7 +1218,7 @@
         <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,45 +1322,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R8" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,6 +1415,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>91366</v>
+        <v>92887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R9" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>92883</v>
+        <v>91370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R10" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129595630</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>92887</v>
+        <v>92889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1215,45 +1215,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595642</v>
+        <v>129595630</v>
       </c>
       <c r="B7" t="n">
-        <v>100969</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707688</v>
+        <v>707781</v>
       </c>
       <c r="R7" t="n">
-        <v>6666281</v>
+        <v>6666273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,49 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595630</v>
+        <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707781</v>
+        <v>707688</v>
       </c>
       <c r="R8" t="n">
-        <v>6666273</v>
+        <v>6666281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1416,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,45 +1108,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R6" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,49 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R7" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>129595642</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B9" t="n">
-        <v>92889</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R9" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B10" t="n">
-        <v>91372</v>
+        <v>92889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R10" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1108,49 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R6" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129595623</v>
+        <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>100979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707785</v>
+        <v>707688</v>
       </c>
       <c r="R7" t="n">
-        <v>6666294</v>
+        <v>6666281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,45 +1322,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595642</v>
+        <v>129595630</v>
       </c>
       <c r="B8" t="n">
-        <v>100979</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707688</v>
+        <v>707781</v>
       </c>
       <c r="R8" t="n">
-        <v>6666281</v>
+        <v>6666273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,6 +1415,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129595623</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129595630</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129595624</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129595628</v>
       </c>
       <c r="B10" t="n">
-        <v>92889</v>
+        <v>92892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B9" t="n">
-        <v>91375</v>
+        <v>92892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R9" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B10" t="n">
-        <v>92892</v>
+        <v>91375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R10" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47951-2025 artfynd.xlsx
+++ b/artfynd/A 47951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595631</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129595622</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129595625</v>
       </c>
       <c r="B4" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129595629</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,45 +1108,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129595623</v>
+        <v>129595630</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707785</v>
+        <v>707781</v>
       </c>
       <c r="R6" t="n">
-        <v>6666294</v>
+        <v>6666273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,7 +1223,7 @@
         <v>129595642</v>
       </c>
       <c r="B7" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,49 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129595630</v>
+        <v>129595623</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>91605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707781</v>
+        <v>707785</v>
       </c>
       <c r="R8" t="n">
-        <v>6666273</v>
+        <v>6666294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1416,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129595628</v>
+        <v>129595624</v>
       </c>
       <c r="B9" t="n">
-        <v>92892</v>
+        <v>91378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2058</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707835</v>
+        <v>707739</v>
       </c>
       <c r="R9" t="n">
-        <v>6666351</v>
+        <v>6666233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129595624</v>
+        <v>129595628</v>
       </c>
       <c r="B10" t="n">
-        <v>91375</v>
+        <v>92895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2058</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707739</v>
+        <v>707835</v>
       </c>
       <c r="R10" t="n">
-        <v>6666233</v>
+        <v>6666351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
